--- a/docs/test-case/integration-test-cases.xlsx
+++ b/docs/test-case/integration-test-cases.xlsx
@@ -8,17 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d375f96120bad62/Desktop/課題対応/家計簿Webアプリ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="8_{91D4A7AF-B525-4A7E-ADD0-9E22A28BA1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E9756FA-F7B1-43A3-A9B3-2C106625A820}"/>
+  <xr:revisionPtr revIDLastSave="446" documentId="8_{91D4A7AF-B525-4A7E-ADD0-9E22A28BA1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4403B52A-1FC5-4F95-89EA-AE3A7F88DCE4}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11100" xr2:uid="{F680F921-48F0-47FF-A86F-48AA68B5DD8F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="781" firstSheet="3" activeTab="7" xr2:uid="{F680F921-48F0-47FF-A86F-48AA68B5DD8F}"/>
   </bookViews>
   <sheets>
     <sheet name="画面・遷移整理" sheetId="1" r:id="rId1"/>
     <sheet name="テストデータ" sheetId="2" r:id="rId2"/>
     <sheet name="テストケース_支出一覧" sheetId="3" r:id="rId3"/>
-    <sheet name="テストケース_支出登録・編集" sheetId="4" r:id="rId4"/>
-    <sheet name="テストケース_予算設定" sheetId="5" r:id="rId5"/>
-    <sheet name="テストケース_トップページ" sheetId="6" r:id="rId6"/>
+    <sheet name="エビデンス_支出一覧" sheetId="7" r:id="rId4"/>
+    <sheet name="テストケース_支出登録・編集" sheetId="4" r:id="rId5"/>
+    <sheet name="エビデンス_支出登録・編集" sheetId="9" r:id="rId6"/>
+    <sheet name="テストケース_予算設定" sheetId="5" r:id="rId7"/>
+    <sheet name="エビデンス_予算設定" sheetId="10" r:id="rId8"/>
+    <sheet name="テストケース_トップページ" sheetId="6" r:id="rId9"/>
+    <sheet name="エビデンス_トップページ" sheetId="11" r:id="rId10"/>
+    <sheet name="不具合一覧表" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="210">
   <si>
     <t>家計簿トップページ /</t>
   </si>
@@ -268,33 +273,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>xx日</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>※テスト日による</t>
-    <rPh sb="4" eb="5">
-      <t>ビ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>食費の週予算</t>
     <rPh sb="0" eb="2">
       <t>ショクヒ</t>
     </rPh>
     <rPh sb="3" eb="6">
       <t>シュウヨサン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>xx円</t>
-    <rPh sb="2" eb="3">
-      <t>エン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -473,14 +457,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>EXP-F07</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EXP-F08</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>店舗名に100文字以上の文字列を入力する</t>
     <rPh sb="0" eb="3">
       <t>テンポメイ</t>
@@ -497,22 +473,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>EXP-F06</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EXP-F09</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EXP-F10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EXP-F11</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>登録されず必須項目のエラーが表示される</t>
     <rPh sb="0" eb="2">
       <t>トウロク</t>
@@ -550,13 +510,6 @@
     <t>満足度を未選択にして登録する</t>
   </si>
   <si>
-    <t>金額に0または負数を入力して登録する</t>
-    <rPh sb="14" eb="16">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>文字数超過のエラーが表示される</t>
     <rPh sb="0" eb="3">
       <t>モジスウ</t>
@@ -592,9 +545,6 @@
     <t>自動計算を押す</t>
   </si>
   <si>
-    <t>食費は週額×10月の土曜日5回、固定額カテゴリは設定額で計算される</t>
-  </si>
-  <si>
     <t>入力欄の金額を変更する</t>
   </si>
   <si>
@@ -619,26 +569,10 @@
     <t>登録されず、入力欄の横にエラーが出る</t>
   </si>
   <si>
-    <t>0または負数を入力して確定する</t>
-  </si>
-  <si>
     <t>別の対象月に切り替える</t>
   </si>
   <si>
     <t>対象月に対応した予算が表示される</t>
-  </si>
-  <si>
-    <t>金額1円以上のエラーが表示される</t>
-    <rPh sb="0" eb="2">
-      <t>キンガク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>エン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>イジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>トップページを表示する</t>
@@ -753,6 +687,92 @@
     <t>テスト当日を基準に残り日数を見る</t>
     <rPh sb="3" eb="5">
       <t>トウジツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「予算設定」を押す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予算設定画面へ遷移する</t>
+    <rPh sb="0" eb="6">
+      <t>ヨサンセッテイガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出登録画面へ遷移する</t>
+    <rPh sb="0" eb="4">
+      <t>シシュツトウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOP-012</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TOP-013</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「支出一覧」を押す</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出一覧画面へ遷移する</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実施結果</t>
+    <rPh sb="0" eb="4">
+      <t>ジッシケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>13日</t>
+    <rPh sb="2" eb="3">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15,000円</t>
+    <rPh sb="6" eb="7">
+      <t>エン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -763,13 +783,13 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>18</t>
+      <t>13</t>
     </r>
     <r>
       <rPr>
@@ -780,34 +800,24 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>日
-（テスト日決定後に日数を記載）</t>
+      <t>日</t>
     </r>
-    <rPh sb="14" eb="18">
-      <t>ビケッテイゴ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ニッスウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>キサイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <r>
-      <t>残り土曜日</t>
+      <t>残り土曜日2回、食費残金30,000円なら</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="游ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>3</t>
+      <t>15,000</t>
     </r>
     <r>
       <rPr>
@@ -818,18 +828,218 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>回、食費残金30,000円なら</t>
+      <t>円</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>負数を入力して確定する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額0円以上のエラーが表示される</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BUD-009</t>
+  </si>
+  <si>
+    <t>金額を0円にして確定する</t>
+    <rPh sb="4" eb="5">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予算が保存され、再表示しても値が残る</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食費は週額×10月の土曜日5回、固定額カテゴリは設定額で計算される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額に0を入力して登録する</t>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額に負数を入力して登録する</t>
+    <rPh sb="10" eb="12">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EXP-F06</t>
+  </si>
+  <si>
+    <t>EXP-F07</t>
+  </si>
+  <si>
+    <t>EXP-F08</t>
+  </si>
+  <si>
+    <t>EXP-F09</t>
+  </si>
+  <si>
+    <t>EXP-F10</t>
+  </si>
+  <si>
+    <t>EXP-F11</t>
+  </si>
+  <si>
+    <t>EXP-F12</t>
+  </si>
+  <si>
+    <t>取得する日付を変更することができないため、実施不可。
+残り土曜日0回の計算自体は単体テストで確認済み。</t>
+    <rPh sb="0" eb="2">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EXP-L02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事象</t>
+    <rPh sb="0" eb="2">
+      <t>ジショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原因</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対応方法</t>
+    <rPh sb="0" eb="4">
+      <t>タイオウホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再テスト</t>
+    <rPh sb="0" eb="1">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合格</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>編集後</t>
+    <rPh sb="0" eb="3">
+      <t>ヘンシュウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>編集前</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EXP-L05</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>削除前</t>
+    <rPh sb="0" eb="3">
+      <t>サクジョマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>削除後</t>
+    <rPh sb="0" eb="3">
+      <t>サクジョゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予算を設定していない月を選択したとき、カテゴリごとの残金が今月の予算額を参照している</t>
+    <rPh sb="0" eb="2">
+      <t>ヨサン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ザンキン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コンゲツ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ヨサンガク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支出一覧画面で表示月の予算を取得する際、選択月の selectedMonth ではなく、現在月の currentMonth を使用していた。そのため、別の月を表示しても今月の予算が残金計算に使われていた。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">予算の取得に </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
       </rPr>
-      <t>10,000</t>
+      <t>selectedMonth</t>
     </r>
     <r>
       <rPr>
@@ -840,111 +1050,75 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>円
-（テスト日決定後に期待結果を記載）</t>
+      <t xml:space="preserve"> を使うよう修正した。表示月に対応した予算で残金が計算されることと、予算未設定の月に今月の予算が表示されないことを確認した。</t>
     </r>
-    <rPh sb="38" eb="42">
-      <t>キタイケッカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「予算設定」を押す</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>予算設定画面へ遷移する</t>
-    <rPh sb="0" eb="6">
-      <t>ヨサンセッテイガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>支出登録画面へ遷移する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不合格
+↓
+合格</t>
+    <rPh sb="0" eb="3">
+      <t>フゴウカク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加前</t>
+    <rPh sb="0" eb="3">
+      <t>ツイカマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加後</t>
+    <rPh sb="0" eb="3">
+      <t>ツイカゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上書き前</t>
+    <rPh sb="0" eb="2">
+      <t>ウワガ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上書き後</t>
+    <rPh sb="0" eb="2">
+      <t>ウワガ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実施不可</t>
     <rPh sb="0" eb="4">
-      <t>シシュツトウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センイ</t>
+      <t>ジッシフカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>TOP-012</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>TOP-013</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「支出一覧」を押す</t>
-    <rPh sb="3" eb="5">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>支出一覧画面へ遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>シシュツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>実施結果</t>
-    <rPh sb="0" eb="4">
-      <t>ジッシケッカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>備考</t>
-    <rPh sb="0" eb="2">
-      <t>ビコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>取得する日付を変更することができないため、実施不可</t>
-    <rPh sb="0" eb="2">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>フカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -996,12 +1170,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1075,7 +1247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1118,6 +1290,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1133,6 +1314,2258 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>56025</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C37841-726D-3656-040C-E254C2745B31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="0"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A964F14B-BAEB-4F8F-9D95-1B0B08B4E06D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="5000625"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6646818C-DB96-40DC-9E0C-8588BAFCE9AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="10477500"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>56025</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B60A72F-77F2-9C8A-2627-9E9B56C24B43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="15716250"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBC1C8DA-2FF9-183E-7A11-AE76E896A0B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="13849350"/>
+          <a:ext cx="2695575" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E86ECD3-C973-4667-A892-BCAA561DEA6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="19069050"/>
+          <a:ext cx="2695575" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A341EFB2-C42B-4FA4-914B-E33596E459E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="21193125"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C049079-0A15-1A9E-6C6F-5C79A1D00F56}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="26431875"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06DD3CAA-F8C5-64D0-2231-595ACF1656F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="31670625"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C815CF9F-10EB-4AC6-8CA5-2C89CF7CE168}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="7581900"/>
+          <a:ext cx="2409825" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>41147</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="吹き出し: 四角形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78B36834-62E6-EA0C-0578-B7DC58CEE530}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3295650" y="7800974"/>
+          <a:ext cx="657225" cy="336423"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -74818"/>
+            <a:gd name="adj2" fmla="val -39769"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>不合格</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>294150</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CED1E73-8F22-6F57-1A82-58C2D7F1E7B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9810750" y="5000625"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{614642FF-67F2-4404-A043-B0CBBD421C13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9829800" y="7581900"/>
+          <a:ext cx="2409825" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20E8050E-5FB6-018F-03B1-129FD7C8FF99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="13" idx="3"/>
+          <a:endCxn id="16" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3095625" y="7691438"/>
+          <a:ext cx="6734175" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04B2594C-7CA2-33F8-2765-84A31696DAB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="238125"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E13DDBC0-5BE1-7D2F-697E-0092C7A7DD67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="5476875"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F31422AF-F9F9-451A-B5B5-EE3E19E82078}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="704850" y="9944100"/>
+          <a:ext cx="2867025" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE23D3E7-80DF-4079-A42E-AC0748ED7B3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="10477500"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>56025</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A7DB30A-B72C-430B-85E7-C53561C26BE5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657225" y="15716250"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DFA2E99-CFB7-4700-9A1C-35AD8F4AD765}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="13849350"/>
+          <a:ext cx="2695575" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8ABA2DE-DA76-4CCA-A253-62C0FFB7FC02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="19069050"/>
+          <a:ext cx="2695575" cy="257175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D593F099-64BB-6AEA-674C-816CC7C0CF82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="21431250"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{655327C8-CFB3-C608-21AC-71BE38C27EF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="26670000"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24C308CE-01AE-1B73-14AD-AA78A3B991C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="31908750"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A50F7527-C507-2D94-A35F-D18C7D841B5A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="37147500"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E9FB3F6-FF51-E206-7F08-77C4F9E0D5EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="42386250"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>200</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07483096-AB1E-DBBB-4360-C878C2920476}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="47625000"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84599</xdr:colOff>
+      <xdr:row>242</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73BF2F87-CD44-64FD-1A3B-5360EC23B318}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685799" y="52863750"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>244</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>264</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53525733-F5FF-B7A0-B039-8A5AF3D6D67A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="58102500"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>266</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>286</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64B44E8C-375E-3676-1F97-6CA0B0BEF7D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="63341250"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>288</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>308</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14F18250-3FE8-5A7D-9238-2F41BA3D1C16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="68580000"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52C74C72-1459-4449-9BB7-4F4600D83BC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="0"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D36D705D-595A-3928-BFED-58A7B64021F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="5238750"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F81DD36-E229-4DA7-1535-81D6DBA2D580}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="10477500"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51063E68-5B10-43B2-9015-59DD3FD9CBDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="15716250"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>101852</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7218F1C4-BE9E-92A2-F52C-58B3F7D1613D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="21193125"/>
+          <a:ext cx="9000000" cy="4626227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>101852</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FFCDDCD-847B-F2CD-5F89-93E352346B22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="26193750"/>
+          <a:ext cx="9000000" cy="4626227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A71C6223-C41F-A698-5366-3329FFF50D91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="31194375"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>173</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E95EAC6E-99B3-2281-2534-530ADC2DBC7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="36433125"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B1CF217-55D1-E5C0-ECF1-420BCB4127E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="41671875"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>217</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD60B283-F419-9515-4F40-8A39FB6EA208}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="46910625"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8004B878-616C-1CCF-1F2D-F57AE52DE562}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="0"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28E942A1-FA58-A210-1635-1DCB715569F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="5238750"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F9D7B3C-B2CC-AC0D-8046-0E2169D59A78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="10477500"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C5D930F-9F8D-6261-29B0-2FA9BDC34299}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="15716250"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>75000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D9F073D-834E-B955-B643-F3893238907C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="20955000"/>
+          <a:ext cx="9000000" cy="4837500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1453,84 +3886,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29AC54F5-F344-4AC4-B9D2-9115C29B1326}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="24">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2">
       <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2">
       <c r="B12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2">
       <c r="B14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2">
       <c r="B16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:2">
       <c r="B17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:2">
       <c r="B18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:2">
       <c r="B19" t="s">
         <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DAAE0C3-958D-4977-A0FA-6FE893F91A93}">
+  <dimension ref="A1:A89"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>209</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B71E043-68F9-48CC-8791-B3A4016CB552}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="3" width="27.75" customWidth="1"/>
+    <col min="4" max="4" width="36.375" customWidth="1"/>
+    <col min="5" max="5" width="48.75" customWidth="1"/>
+    <col min="6" max="6" width="50.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="75">
+      <c r="A2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1542,7 +4110,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{039C153C-7126-4968-8EE7-AAEA2C0A8E64}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
@@ -1551,12 +4119,12 @@
     <col min="5" max="5" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="24">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6">
       <c r="B2" s="4" t="s">
         <v>34</v>
       </c>
@@ -1573,7 +4141,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6">
       <c r="B3" s="2">
         <v>46309</v>
       </c>
@@ -1590,7 +4158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6">
       <c r="B4" s="2">
         <v>46310</v>
       </c>
@@ -1607,7 +4175,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6">
       <c r="B5" s="2">
         <v>46311</v>
       </c>
@@ -1624,7 +4192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6">
       <c r="B6" s="2">
         <v>46312</v>
       </c>
@@ -1641,7 +4209,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6">
       <c r="B7" s="2">
         <v>46313</v>
       </c>
@@ -1658,7 +4226,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6">
       <c r="B8" s="2">
         <v>46314</v>
       </c>
@@ -1675,12 +4243,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="24">
       <c r="A11" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6">
       <c r="B12" s="4" t="s">
         <v>50</v>
       </c>
@@ -1694,7 +4262,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6">
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
@@ -1708,7 +4276,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6">
       <c r="B14" s="3" t="s">
         <v>23</v>
       </c>
@@ -1722,7 +4290,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6">
       <c r="B15" s="3" t="s">
         <v>26</v>
       </c>
@@ -1736,7 +4304,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6">
       <c r="B16" s="3" t="s">
         <v>29</v>
       </c>
@@ -1750,7 +4318,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" ht="19.5" thickBot="1">
       <c r="B17" s="7" t="s">
         <v>32</v>
       </c>
@@ -1764,7 +4332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" ht="19.5" thickTop="1">
       <c r="B18" s="8" t="s">
         <v>46</v>
       </c>
@@ -1778,20 +4346,20 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="25.5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" ht="25.5">
       <c r="A21" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="B22" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="B23" s="10" t="s">
         <v>52</v>
       </c>
@@ -1799,7 +4367,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5">
       <c r="B24" s="10" t="s">
         <v>53</v>
       </c>
@@ -1807,42 +4375,36 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5">
       <c r="B25" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C25" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="B26" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D25" t="s">
+      <c r="C26" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="B27" s="10" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B26" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B27" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="C27" s="11">
         <v>0.73</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" ht="37.5">
       <c r="B28" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1854,117 +4416,131 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834A3259-BDCD-4F9E-8144-6B393F566537}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="3" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="37.5">
+      <c r="A2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" ht="56.25">
+      <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" ht="37.5">
+      <c r="A5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" ht="37.5">
+      <c r="A6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" ht="37.5">
+      <c r="A7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="10"/>
+      <c r="D8" s="14" t="s">
+        <v>193</v>
+      </c>
       <c r="E8" s="10"/>
     </row>
   </sheetData>
@@ -1974,308 +4550,273 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA80323C-4604-4C16-9EA5-2631E897E515}">
+  <dimension ref="A1:B134"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>196</v>
+      </c>
+      <c r="B89" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F278CD39-C670-4B04-A1FE-81E7BE595718}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="28.25" customWidth="1"/>
     <col min="3" max="3" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="37.5">
+      <c r="A2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" ht="37.5">
+      <c r="A3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" ht="37.5">
+      <c r="A4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" ht="37.5">
+      <c r="A5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" ht="37.5">
+      <c r="A6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" ht="37.5">
+      <c r="A7" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5" ht="37.5">
+      <c r="A8" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="B8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" ht="37.5">
+      <c r="A9" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" ht="37.5">
+      <c r="A10" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" ht="37.5">
+      <c r="A11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:5" ht="37.5">
+      <c r="A12" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:5" ht="37.5">
+      <c r="A13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A12" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B693036-C36B-4D4C-A903-1AF888DF7F6F}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="3" width="30.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
+      <c r="D13" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -2284,200 +4825,545 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5807D3B2-4967-4ABA-9122-D0EF83D5BE37}">
+  <dimension ref="A1:B289"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B693036-C36B-4D4C-A903-1AF888DF7F6F}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="3" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="37.5">
+      <c r="A2" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" ht="37.5">
+      <c r="A3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" ht="37.5">
+      <c r="A4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" ht="37.5">
+      <c r="A5" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" ht="37.5">
+      <c r="A6" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" ht="37.5">
+      <c r="A7" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" ht="37.5">
+      <c r="A9" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="10"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C320D6D1-DDA1-45A7-BE78-DBB4044CC9F1}">
+  <dimension ref="A1:B198"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>153</v>
+      </c>
+      <c r="B89" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{808CC8B2-2F7C-47AC-B423-95574BCE7350}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="3" width="35.625" customWidth="1"/>
     <col min="5" max="5" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" ht="37.5">
+      <c r="A3" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" ht="37.5">
+      <c r="A5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" ht="75">
+      <c r="A6" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="37.5">
+      <c r="A7" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5" ht="37.5">
+      <c r="A8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" ht="37.5">
+      <c r="A9" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" ht="37.5">
+      <c r="A10" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D10" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" ht="37.5">
+      <c r="A11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:5" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="14" t="s">
+        <v>193</v>
+      </c>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="10"/>
+        <v>165</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>193</v>
+      </c>
       <c r="E14" s="10"/>
     </row>
   </sheetData>
